--- a/Modul_5/src/main/resources/data_mahasiswa.xlsx
+++ b/Modul_5/src/main/resources/data_mahasiswa.xlsx
@@ -23,16 +23,16 @@
     <t>Mata Kuliah</t>
   </si>
   <si>
-    <t>Radya</t>
+    <t>radya</t>
   </si>
   <si>
-    <t>Informatika</t>
+    <t>pemlan</t>
   </si>
   <si>
-    <t>Aini</t>
+    <t>muhammad</t>
   </si>
   <si>
-    <t>Data Science</t>
+    <t>alpro</t>
   </si>
 </sst>
 </file>
